--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.39814942792015</v>
+        <v>3.964699282037025</v>
       </c>
       <c r="D2" t="n">
-        <v>25.78028274900842</v>
+        <v>4.18929594671387</v>
       </c>
       <c r="E2" t="n">
-        <v>10.83795824998447</v>
+        <v>1.761168215622475</v>
       </c>
       <c r="F2" t="n">
-        <v>10.60135225772834</v>
+        <v>1.722719741880855</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.32540108295999</v>
+        <v>5.415377675980999</v>
       </c>
       <c r="D3" t="n">
-        <v>34.45436475208326</v>
+        <v>5.59883427221353</v>
       </c>
       <c r="E3" t="n">
-        <v>10.83795824998447</v>
+        <v>1.761168215622475</v>
       </c>
       <c r="F3" t="n">
-        <v>10.60135225772834</v>
+        <v>1.722719741880855</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.63511534111556</v>
+        <v>5.628206242931278</v>
       </c>
       <c r="D4" t="n">
-        <v>34.62457022328698</v>
+        <v>5.626492661284135</v>
       </c>
       <c r="E4" t="n">
-        <v>10.83795824998447</v>
+        <v>1.761168215622475</v>
       </c>
       <c r="F4" t="n">
-        <v>10.60135225772834</v>
+        <v>1.722719741880855</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.468804296020847</v>
+        <v>1.213680698103388</v>
       </c>
       <c r="D5" t="n">
-        <v>8.572213976543482</v>
+        <v>1.392984771188316</v>
       </c>
       <c r="E5" t="n">
-        <v>10.83795824998447</v>
+        <v>1.761168215622475</v>
       </c>
       <c r="F5" t="n">
-        <v>10.60135225772834</v>
+        <v>1.722719741880855</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
